--- a/artfynd/A 26898-2022 artfynd.xlsx
+++ b/artfynd/A 26898-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26898-2022 artfynd.xlsx
+++ b/artfynd/A 26898-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95974179</v>
+        <v>95974181</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329871.2186890794</v>
+        <v>329841</v>
       </c>
       <c r="R2" t="n">
-        <v>6624268.578280342</v>
+        <v>6624313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95974182</v>
+        <v>95974186</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329824.3398259885</v>
+        <v>329825</v>
       </c>
       <c r="R3" t="n">
-        <v>6624350.019113348</v>
+        <v>6624346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95974181</v>
+        <v>97748907</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -935,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skårsjön, Vrm</t>
+          <t>V om Stötterud, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329840.8597671414</v>
+        <v>329832</v>
       </c>
       <c r="R4" t="n">
-        <v>6624312.897850359</v>
+        <v>6624302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,31 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95974186</v>
+        <v>97748912</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1047,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skårsjön, Vrm</t>
+          <t>V om Stötterud, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329825.1655397578</v>
+        <v>329657</v>
       </c>
       <c r="R5" t="n">
-        <v>6624345.940646674</v>
+        <v>6624311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97748922</v>
+        <v>97748916</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>329856.8994137132</v>
+        <v>329707</v>
       </c>
       <c r="R6" t="n">
-        <v>6624287.415653341</v>
+        <v>6624272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97748916</v>
+        <v>97748922</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>329707.4636932669</v>
+        <v>329857</v>
       </c>
       <c r="R7" t="n">
-        <v>6624272.520370906</v>
+        <v>6624287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97748907</v>
+        <v>95974179</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V om Stötterud, Vrm</t>
+          <t>Skårsjön, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>329831.7699757289</v>
+        <v>329871</v>
       </c>
       <c r="R8" t="n">
-        <v>6624302.200598658</v>
+        <v>6624268</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1342,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1462,16 +1357,11 @@
         <v>97748921</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330037.9126316003</v>
+        <v>330038</v>
       </c>
       <c r="R9" t="n">
-        <v>6624284.713475327</v>
+        <v>6624284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,50 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97748912</v>
+        <v>95974182</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>V om Stötterud, Vrm</t>
+          <t>Skårsjön, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>329656.5876367373</v>
+        <v>329824</v>
       </c>
       <c r="R10" t="n">
-        <v>6624310.707591974</v>
+        <v>6624350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,15 +1536,218 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95974178</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skårsjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>329751</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6624390</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97748909</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>V om Stötterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>329682</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6624283</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26898-2022 artfynd.xlsx
+++ b/artfynd/A 26898-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95974181</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95974186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748907</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95974179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748921</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95974182</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95974178</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,8 +1803,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748909</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>